--- a/Projektplanung/Bearbeitungsplan_ueberarbeitet.xlsx
+++ b/Projektplanung/Bearbeitungsplan_ueberarbeitet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masterarbeit NO-Surrogate for SC simulations\Neural Operator for Cheetah\Projektplanung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385EBB41-997E-4F68-A8E0-94569D5C9D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4294EFD5-9D85-457A-A352-3AB3DA998D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bearbeitungsplan" sheetId="1" r:id="rId1"/>
@@ -953,7 +953,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1013,6 +1013,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1121,7 +1133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1206,51 +1218,54 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1569,7 +1584,7 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="56" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="51"/>
@@ -1578,7 +1593,7 @@
       <c r="K1" s="51"/>
       <c r="L1" s="51"/>
       <c r="M1" s="51"/>
-      <c r="N1" s="60" t="s">
+      <c r="N1" s="56" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="51"/>
@@ -1587,7 +1602,7 @@
       <c r="R1" s="51"/>
       <c r="S1" s="51"/>
       <c r="T1" s="51"/>
-      <c r="U1" s="60" t="s">
+      <c r="U1" s="56" t="s">
         <v>3</v>
       </c>
       <c r="V1" s="51"/>
@@ -1596,7 +1611,7 @@
       <c r="Y1" s="51"/>
       <c r="Z1" s="51"/>
       <c r="AA1" s="51"/>
-      <c r="AB1" s="64" t="s">
+      <c r="AB1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="AC1" s="51"/>
@@ -1605,7 +1620,7 @@
       <c r="AF1" s="51"/>
       <c r="AG1" s="51"/>
       <c r="AH1" s="51"/>
-      <c r="AI1" s="60" t="s">
+      <c r="AI1" s="56" t="s">
         <v>5</v>
       </c>
       <c r="AJ1" s="51"/>
@@ -1614,7 +1629,7 @@
       <c r="AM1" s="51"/>
       <c r="AN1" s="51"/>
       <c r="AO1" s="51"/>
-      <c r="AP1" s="60" t="s">
+      <c r="AP1" s="56" t="s">
         <v>6</v>
       </c>
       <c r="AQ1" s="51"/>
@@ -1623,7 +1638,7 @@
       <c r="AT1" s="51"/>
       <c r="AU1" s="51"/>
       <c r="AV1" s="51"/>
-      <c r="AW1" s="60" t="s">
+      <c r="AW1" s="56" t="s">
         <v>7</v>
       </c>
       <c r="AX1" s="51"/>
@@ -1632,7 +1647,7 @@
       <c r="BA1" s="51"/>
       <c r="BB1" s="51"/>
       <c r="BC1" s="51"/>
-      <c r="BD1" s="60" t="s">
+      <c r="BD1" s="56" t="s">
         <v>8</v>
       </c>
       <c r="BE1" s="51"/>
@@ -1641,7 +1656,7 @@
       <c r="BH1" s="51"/>
       <c r="BI1" s="51"/>
       <c r="BJ1" s="51"/>
-      <c r="BK1" s="60" t="s">
+      <c r="BK1" s="56" t="s">
         <v>9</v>
       </c>
       <c r="BL1" s="51"/>
@@ -1650,7 +1665,7 @@
       <c r="BO1" s="51"/>
       <c r="BP1" s="51"/>
       <c r="BQ1" s="51"/>
-      <c r="BR1" s="60" t="s">
+      <c r="BR1" s="56" t="s">
         <v>10</v>
       </c>
       <c r="BS1" s="51"/>
@@ -1659,7 +1674,7 @@
       <c r="BV1" s="51"/>
       <c r="BW1" s="51"/>
       <c r="BX1" s="51"/>
-      <c r="BY1" s="60" t="s">
+      <c r="BY1" s="56" t="s">
         <v>11</v>
       </c>
       <c r="BZ1" s="51"/>
@@ -1668,7 +1683,7 @@
       <c r="CC1" s="51"/>
       <c r="CD1" s="51"/>
       <c r="CE1" s="51"/>
-      <c r="CF1" s="60" t="s">
+      <c r="CF1" s="56" t="s">
         <v>12</v>
       </c>
       <c r="CG1" s="51"/>
@@ -1677,7 +1692,7 @@
       <c r="CJ1" s="51"/>
       <c r="CK1" s="51"/>
       <c r="CL1" s="51"/>
-      <c r="CM1" s="60" t="s">
+      <c r="CM1" s="56" t="s">
         <v>13</v>
       </c>
       <c r="CN1" s="51"/>
@@ -1686,7 +1701,7 @@
       <c r="CQ1" s="51"/>
       <c r="CR1" s="51"/>
       <c r="CS1" s="51"/>
-      <c r="CT1" s="60" t="s">
+      <c r="CT1" s="56" t="s">
         <v>14</v>
       </c>
       <c r="CU1" s="51"/>
@@ -1695,7 +1710,7 @@
       <c r="CX1" s="51"/>
       <c r="CY1" s="51"/>
       <c r="CZ1" s="51"/>
-      <c r="DA1" s="60" t="s">
+      <c r="DA1" s="56" t="s">
         <v>15</v>
       </c>
       <c r="DB1" s="51"/>
@@ -1704,7 +1719,7 @@
       <c r="DE1" s="51"/>
       <c r="DF1" s="51"/>
       <c r="DG1" s="51"/>
-      <c r="DH1" s="60" t="s">
+      <c r="DH1" s="56" t="s">
         <v>16</v>
       </c>
       <c r="DI1" s="51"/>
@@ -1713,7 +1728,7 @@
       <c r="DL1" s="51"/>
       <c r="DM1" s="51"/>
       <c r="DN1" s="51"/>
-      <c r="DO1" s="60" t="s">
+      <c r="DO1" s="56" t="s">
         <v>17</v>
       </c>
       <c r="DP1" s="51"/>
@@ -1722,7 +1737,7 @@
       <c r="DS1" s="51"/>
       <c r="DT1" s="51"/>
       <c r="DU1" s="51"/>
-      <c r="DV1" s="60" t="s">
+      <c r="DV1" s="56" t="s">
         <v>18</v>
       </c>
       <c r="DW1" s="51"/>
@@ -1731,7 +1746,7 @@
       <c r="DZ1" s="51"/>
       <c r="EA1" s="51"/>
       <c r="EB1" s="51"/>
-      <c r="EC1" s="60" t="s">
+      <c r="EC1" s="56" t="s">
         <v>19</v>
       </c>
       <c r="ED1" s="51"/>
@@ -1740,7 +1755,7 @@
       <c r="EG1" s="51"/>
       <c r="EH1" s="51"/>
       <c r="EI1" s="51"/>
-      <c r="EJ1" s="60" t="s">
+      <c r="EJ1" s="56" t="s">
         <v>20</v>
       </c>
       <c r="EK1" s="51"/>
@@ -1749,7 +1764,7 @@
       <c r="EN1" s="51"/>
       <c r="EO1" s="51"/>
       <c r="EP1" s="51"/>
-      <c r="EQ1" s="60" t="s">
+      <c r="EQ1" s="56" t="s">
         <v>21</v>
       </c>
       <c r="ER1" s="51"/>
@@ -1758,7 +1773,7 @@
       <c r="EU1" s="51"/>
       <c r="EV1" s="51"/>
       <c r="EW1" s="51"/>
-      <c r="EX1" s="60" t="s">
+      <c r="EX1" s="56" t="s">
         <v>22</v>
       </c>
       <c r="EY1" s="51"/>
@@ -1767,7 +1782,7 @@
       <c r="FB1" s="51"/>
       <c r="FC1" s="51"/>
       <c r="FD1" s="51"/>
-      <c r="FE1" s="60" t="s">
+      <c r="FE1" s="56" t="s">
         <v>23</v>
       </c>
       <c r="FF1" s="51"/>
@@ -1776,7 +1791,7 @@
       <c r="FI1" s="51"/>
       <c r="FJ1" s="51"/>
       <c r="FK1" s="51"/>
-      <c r="FL1" s="60" t="s">
+      <c r="FL1" s="56" t="s">
         <v>24</v>
       </c>
       <c r="FM1" s="51"/>
@@ -1785,7 +1800,7 @@
       <c r="FP1" s="51"/>
       <c r="FQ1" s="51"/>
       <c r="FR1" s="51"/>
-      <c r="FS1" s="60" t="s">
+      <c r="FS1" s="56" t="s">
         <v>25</v>
       </c>
       <c r="FT1" s="51"/>
@@ -1794,7 +1809,7 @@
       <c r="FW1" s="51"/>
       <c r="FX1" s="51"/>
       <c r="FY1" s="51"/>
-      <c r="FZ1" s="60" t="s">
+      <c r="FZ1" s="56" t="s">
         <v>26</v>
       </c>
       <c r="GA1" s="51"/>
@@ -1803,7 +1818,7 @@
       <c r="GD1" s="51"/>
       <c r="GE1" s="51"/>
       <c r="GF1" s="51"/>
-      <c r="GG1" s="60" t="s">
+      <c r="GG1" s="56" t="s">
         <v>27</v>
       </c>
       <c r="GH1" s="51"/>
@@ -1812,7 +1827,7 @@
       <c r="GK1" s="51"/>
       <c r="GL1" s="51"/>
       <c r="GM1" s="51"/>
-      <c r="GN1" s="60" t="s">
+      <c r="GN1" s="56" t="s">
         <v>28</v>
       </c>
       <c r="GO1" s="51"/>
@@ -1821,7 +1836,7 @@
       <c r="GR1" s="51"/>
       <c r="GS1" s="51"/>
       <c r="GT1" s="51"/>
-      <c r="GU1" s="60" t="s">
+      <c r="GU1" s="56" t="s">
         <v>29</v>
       </c>
       <c r="GV1" s="51"/>
@@ -1830,7 +1845,7 @@
       <c r="GY1" s="51"/>
       <c r="GZ1" s="51"/>
       <c r="HA1" s="51"/>
-      <c r="HB1" s="60" t="s">
+      <c r="HB1" s="56" t="s">
         <v>30</v>
       </c>
       <c r="HC1" s="51"/>
@@ -1839,7 +1854,7 @@
       <c r="HF1" s="51"/>
       <c r="HG1" s="51"/>
       <c r="HH1" s="51"/>
-      <c r="HI1" s="60" t="s">
+      <c r="HI1" s="56" t="s">
         <v>31</v>
       </c>
       <c r="HJ1" s="51"/>
@@ -1848,7 +1863,7 @@
       <c r="HM1" s="51"/>
       <c r="HN1" s="51"/>
       <c r="HO1" s="51"/>
-      <c r="HP1" s="60" t="s">
+      <c r="HP1" s="56" t="s">
         <v>32</v>
       </c>
       <c r="HQ1" s="51"/>
@@ -3423,20 +3438,20 @@
       <c r="HR4" s="7"/>
     </row>
     <row r="5" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="53" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="65" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="61"/>
+      <c r="F5" s="60"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="11"/>
@@ -3659,14 +3674,14 @@
       <c r="HR5" s="11"/>
     </row>
     <row r="6" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
       <c r="D6" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
       <c r="G6" s="11"/>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
@@ -3889,18 +3904,18 @@
       <c r="HR6" s="11"/>
     </row>
     <row r="7" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="53" t="s">
+      <c r="A7" s="59"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="65" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="61"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="11"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
@@ -4123,14 +4138,14 @@
       <c r="HR7" s="11"/>
     </row>
     <row r="8" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
       <c r="D8" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -4353,18 +4368,18 @@
       <c r="HR8" s="11"/>
     </row>
     <row r="9" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="53" t="s">
+      <c r="A9" s="59"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="65" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="61"/>
+      <c r="F9" s="60"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -4587,14 +4602,14 @@
       <c r="HR9" s="11"/>
     </row>
     <row r="10" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -4817,18 +4832,18 @@
       <c r="HR10" s="11"/>
     </row>
     <row r="11" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="53" t="s">
+      <c r="A11" s="59"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="65" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="60"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -5051,14 +5066,14 @@
       <c r="HR11" s="11"/>
     </row>
     <row r="12" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -5281,18 +5296,18 @@
       <c r="HR12" s="11"/>
     </row>
     <row r="13" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="54"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="53" t="s">
+      <c r="A13" s="59"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="65" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -5515,14 +5530,14 @@
       <c r="HR13" s="11"/>
     </row>
     <row r="14" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -5745,18 +5760,18 @@
       <c r="HR14" s="11"/>
     </row>
     <row r="15" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="54"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="53" t="s">
+      <c r="A15" s="59"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="65" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="61"/>
+      <c r="F15" s="60"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -5979,14 +5994,14 @@
       <c r="HR15" s="11"/>
     </row>
     <row r="16" spans="1:226" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -6209,18 +6224,18 @@
       <c r="HR16" s="11"/>
     </row>
     <row r="17" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="54"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="53" t="s">
+      <c r="A17" s="59"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="65" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="61"/>
+      <c r="F17" s="60"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -6443,14 +6458,14 @@
       <c r="HR17" s="11"/>
     </row>
     <row r="18" spans="1:227" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -6673,18 +6688,18 @@
       <c r="HR18" s="11"/>
     </row>
     <row r="19" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="53" t="s">
+      <c r="A19" s="59"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="65" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="61"/>
+      <c r="F19" s="60"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
@@ -6907,14 +6922,14 @@
       <c r="HR19" s="11"/>
     </row>
     <row r="20" spans="1:227" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -7137,18 +7152,18 @@
       <c r="HR20" s="11"/>
     </row>
     <row r="21" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="54"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="53" t="s">
+      <c r="A21" s="59"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="65" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="63" t="s">
+      <c r="E21" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="61"/>
+      <c r="F21" s="60"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
@@ -7371,14 +7386,14 @@
       <c r="HR21" s="11"/>
     </row>
     <row r="22" spans="1:227" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="62"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
+      <c r="A22" s="63"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
       <c r="D22" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
       <c r="G22" s="44"/>
       <c r="H22" s="44"/>
       <c r="I22" s="44"/>
@@ -7601,22 +7616,22 @@
       <c r="HR22" s="44"/>
     </row>
     <row r="23" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="54" t="s">
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="57" t="s">
+      <c r="F23" s="55" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="11"/>
@@ -8072,19 +8087,19 @@
     </row>
     <row r="25" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="51"/>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="55" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="11"/>
@@ -8538,19 +8553,19 @@
     </row>
     <row r="27" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="51"/>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="61" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="57"/>
+      <c r="F27" s="55"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -9003,22 +9018,22 @@
       <c r="HR28" s="11"/>
     </row>
     <row r="29" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="54" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G29" s="11"/>
@@ -9277,7 +9292,7 @@
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
       <c r="AF30" s="12"/>
-      <c r="AG30" s="13"/>
+      <c r="AG30" s="69"/>
       <c r="AH30" s="14"/>
       <c r="AI30" s="11"/>
       <c r="AJ30" s="11"/>
@@ -9474,19 +9489,19 @@
     </row>
     <row r="31" spans="1:227" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="54" t="s">
         <v>82</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="57" t="s">
+      <c r="F31" s="55" t="s">
         <v>3</v>
       </c>
       <c r="G31" s="11"/>
@@ -9942,19 +9957,19 @@
     </row>
     <row r="33" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="51"/>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="54" t="s">
         <v>85</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="11"/>
@@ -10410,19 +10425,19 @@
     </row>
     <row r="35" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51"/>
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="54" t="s">
         <v>88</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="55" t="s">
+      <c r="E35" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G35" s="11"/>
@@ -10878,19 +10893,19 @@
     </row>
     <row r="37" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="51"/>
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="54" t="s">
         <v>91</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="55" t="s">
+      <c r="E37" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="55" t="s">
         <v>3</v>
       </c>
       <c r="G37" s="11"/>
@@ -11346,19 +11361,19 @@
     </row>
     <row r="39" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="51"/>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="52" t="s">
+      <c r="C39" s="54" t="s">
         <v>94</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="55" t="s">
+      <c r="E39" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="F39" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G39" s="11"/>
@@ -11813,22 +11828,22 @@
       <c r="HR40" s="11"/>
     </row>
     <row r="41" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="52" t="s">
+      <c r="C41" s="54" t="s">
         <v>98</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="55" t="s">
+      <c r="E41" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G41" s="11"/>
@@ -12082,10 +12097,10 @@
       <c r="Y42" s="12"/>
       <c r="Z42" s="13"/>
       <c r="AA42" s="14"/>
-      <c r="AB42" s="15"/>
-      <c r="AC42" s="11"/>
-      <c r="AD42" s="11"/>
-      <c r="AE42" s="11"/>
+      <c r="AB42" s="67"/>
+      <c r="AC42" s="68"/>
+      <c r="AD42" s="69"/>
+      <c r="AE42" s="69"/>
       <c r="AF42" s="12"/>
       <c r="AG42" s="13"/>
       <c r="AH42" s="14"/>
@@ -12284,19 +12299,19 @@
     </row>
     <row r="43" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="52" t="s">
+      <c r="C43" s="54" t="s">
         <v>101</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E43" s="55" t="s">
+      <c r="E43" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="F43" s="57" t="s">
+      <c r="F43" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G43" s="11"/>
@@ -12752,19 +12767,19 @@
     </row>
     <row r="45" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="51"/>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="54" t="s">
         <v>104</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="55" t="s">
+      <c r="E45" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="F45" s="57" t="s">
+      <c r="F45" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G45" s="11"/>
@@ -13219,22 +13234,22 @@
       <c r="HR46" s="11"/>
     </row>
     <row r="47" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="54" t="s">
         <v>108</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="55" t="s">
+      <c r="E47" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="F47" s="57" t="s">
+      <c r="F47" s="55" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="11"/>
@@ -13690,19 +13705,19 @@
     </row>
     <row r="49" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="51"/>
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="54" t="s">
         <v>111</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E49" s="55" t="s">
+      <c r="E49" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G49" s="11"/>
@@ -14157,22 +14172,22 @@
       <c r="HR50" s="11"/>
     </row>
     <row r="51" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="54" t="s">
         <v>115</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="55" t="s">
+      <c r="E51" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="F51" s="57" t="s">
+      <c r="F51" s="55" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="11"/>
@@ -14628,19 +14643,19 @@
     </row>
     <row r="53" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="51"/>
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="52" t="s">
+      <c r="C53" s="54" t="s">
         <v>118</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E53" s="55" t="s">
+      <c r="E53" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="55" t="s">
         <v>6</v>
       </c>
       <c r="G53" s="11"/>
@@ -15095,22 +15110,22 @@
       <c r="HR54" s="11"/>
     </row>
     <row r="55" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="50" t="s">
+      <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="C55" s="52" t="s">
+      <c r="C55" s="54" t="s">
         <v>122</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E55" s="55" t="s">
+      <c r="E55" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="57" t="s">
+      <c r="F55" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G55" s="11"/>
@@ -15566,19 +15581,19 @@
     </row>
     <row r="57" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="51"/>
-      <c r="B57" s="56" t="s">
+      <c r="B57" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="52" t="s">
+      <c r="C57" s="54" t="s">
         <v>125</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E57" s="55" t="s">
+      <c r="E57" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G57" s="11"/>
@@ -16034,19 +16049,19 @@
     </row>
     <row r="59" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="51"/>
-      <c r="B59" s="56" t="s">
+      <c r="B59" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="C59" s="52" t="s">
+      <c r="C59" s="54" t="s">
         <v>128</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="55" t="s">
+      <c r="E59" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="F59" s="57" t="s">
+      <c r="F59" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G59" s="11"/>
@@ -16502,19 +16517,19 @@
     </row>
     <row r="61" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="51"/>
-      <c r="B61" s="56" t="s">
+      <c r="B61" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="52" t="s">
+      <c r="C61" s="54" t="s">
         <v>131</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="55" t="s">
+      <c r="E61" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G61" s="11"/>
@@ -16970,19 +16985,19 @@
     </row>
     <row r="63" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="51"/>
-      <c r="B63" s="56" t="s">
+      <c r="B63" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="54" t="s">
         <v>134</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E63" s="55" t="s">
+      <c r="E63" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="57" t="s">
+      <c r="F63" s="55" t="s">
         <v>7</v>
       </c>
       <c r="G63" s="11"/>
@@ -17438,19 +17453,19 @@
     </row>
     <row r="65" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="51"/>
-      <c r="B65" s="56" t="s">
+      <c r="B65" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="52" t="s">
+      <c r="C65" s="54" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E65" s="55" t="s">
+      <c r="E65" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G65" s="11"/>
@@ -17905,22 +17920,22 @@
       <c r="HR66" s="11"/>
     </row>
     <row r="67" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="50" t="s">
+      <c r="A67" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="56" t="s">
+      <c r="B67" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="52" t="s">
+      <c r="C67" s="54" t="s">
         <v>141</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E67" s="55" t="s">
+      <c r="E67" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="F67" s="57" t="s">
+      <c r="F67" s="55" t="s">
         <v>3</v>
       </c>
       <c r="G67" s="11"/>
@@ -18376,19 +18391,19 @@
     </row>
     <row r="69" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="51"/>
-      <c r="B69" s="56" t="s">
+      <c r="B69" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="52" t="s">
+      <c r="C69" s="54" t="s">
         <v>144</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E69" s="55" t="s">
+      <c r="E69" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="55" t="s">
         <v>70</v>
       </c>
       <c r="G69" s="11"/>
@@ -18844,19 +18859,19 @@
     </row>
     <row r="71" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="51"/>
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="C71" s="52" t="s">
+      <c r="C71" s="54" t="s">
         <v>147</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E71" s="55" t="s">
+      <c r="E71" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F71" s="55" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="11"/>
@@ -19312,19 +19327,19 @@
     </row>
     <row r="73" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="51"/>
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="C73" s="52" t="s">
+      <c r="C73" s="54" t="s">
         <v>150</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E73" s="55" t="s">
+      <c r="E73" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="F73" s="57" t="s">
+      <c r="F73" s="55" t="s">
         <v>14</v>
       </c>
       <c r="G73" s="11"/>
@@ -19780,19 +19795,19 @@
     </row>
     <row r="75" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="51"/>
-      <c r="B75" s="56" t="s">
+      <c r="B75" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="C75" s="52" t="s">
+      <c r="C75" s="54" t="s">
         <v>153</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E75" s="55" t="s">
+      <c r="E75" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="F75" s="57" t="s">
+      <c r="F75" s="55" t="s">
         <v>8</v>
       </c>
       <c r="G75" s="11"/>
@@ -20248,19 +20263,19 @@
     </row>
     <row r="77" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="51"/>
-      <c r="B77" s="56" t="s">
+      <c r="B77" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="52" t="s">
+      <c r="C77" s="54" t="s">
         <v>156</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E77" s="55" t="s">
+      <c r="E77" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="57" t="s">
+      <c r="F77" s="55" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="11"/>
@@ -20715,22 +20730,22 @@
       <c r="HR78" s="11"/>
     </row>
     <row r="79" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
+      <c r="A79" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="56" t="s">
+      <c r="B79" s="52" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="58" t="s">
+      <c r="C79" s="50" t="s">
         <v>160</v>
       </c>
       <c r="D79" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E79" s="55" t="s">
+      <c r="E79" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="F79" s="57" t="s">
+      <c r="F79" s="55" t="s">
         <v>13</v>
       </c>
       <c r="G79" s="11"/>
@@ -21186,19 +21201,19 @@
     </row>
     <row r="81" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="51"/>
-      <c r="B81" s="56" t="s">
+      <c r="B81" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="58" t="s">
+      <c r="C81" s="50" t="s">
         <v>163</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E81" s="55" t="s">
+      <c r="E81" s="53" t="s">
         <v>164</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="55" t="s">
         <v>8</v>
       </c>
       <c r="G81" s="11"/>
@@ -21654,19 +21669,19 @@
     </row>
     <row r="83" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="51"/>
-      <c r="B83" s="56" t="s">
+      <c r="B83" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="C83" s="52" t="s">
+      <c r="C83" s="54" t="s">
         <v>166</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="55" t="s">
+      <c r="E83" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="F83" s="57" t="s">
+      <c r="F83" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G83" s="11"/>
@@ -22122,19 +22137,19 @@
     </row>
     <row r="85" spans="1:226" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="51"/>
-      <c r="B85" s="56" t="s">
+      <c r="B85" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="65" t="s">
+      <c r="C85" s="61" t="s">
         <v>169</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E85" s="55" t="s">
+      <c r="E85" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="F85" s="57"/>
+      <c r="F85" s="55"/>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
       <c r="I85" s="11"/>
@@ -22588,38 +22603,139 @@
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="GU1:HA1"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="FE1:FK1"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="HI1:HO1"/>
-    <mergeCell ref="A67:A78"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="FZ1:GF1"/>
-    <mergeCell ref="EX1:FD1"/>
-    <mergeCell ref="HB1:HH1"/>
-    <mergeCell ref="CM1:CS1"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="U1:AA1"/>
-    <mergeCell ref="BY1:CE1"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A79:A86"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="GN1:GT1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="BD1:BJ1"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="FS1:FY1"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="HP1:HR1"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="EJ1:EP1"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="DH1:DN1"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="FL1:FR1"/>
+    <mergeCell ref="DV1:EB1"/>
+    <mergeCell ref="EC1:EI1"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="DA1:DG1"/>
+    <mergeCell ref="N1:T1"/>
+    <mergeCell ref="CT1:CZ1"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="DO1:DU1"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="AI1:AO1"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A29:A40"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="A5:A22"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A55:A66"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="F17:F18"/>
     <mergeCell ref="F81:F82"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="B15:B16"/>
@@ -22644,30 +22760,23 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="AW1:BC1"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A29:A40"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="A5:A22"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A55:A66"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="HI1:HO1"/>
+    <mergeCell ref="A67:A78"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="FZ1:GF1"/>
+    <mergeCell ref="EX1:FD1"/>
+    <mergeCell ref="HB1:HH1"/>
+    <mergeCell ref="CM1:CS1"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="BY1:CE1"/>
     <mergeCell ref="GG1:GM1"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="C51:C52"/>
@@ -22675,6 +22784,21 @@
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="F61:F62"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="GU1:HA1"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="FE1:FK1"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="EQ1:EW1"/>
     <mergeCell ref="B55:B56"/>
     <mergeCell ref="AB1:AH1"/>
@@ -22684,115 +22808,6 @@
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="AP1:AV1"/>
     <mergeCell ref="E59:E60"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="DO1:DU1"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="FS1:FY1"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="HP1:HR1"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="EJ1:EP1"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="DH1:DN1"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="FL1:FR1"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="DV1:EB1"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="EC1:EI1"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="DA1:DG1"/>
-    <mergeCell ref="N1:T1"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="CT1:CZ1"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="AI1:AO1"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="GN1:GT1"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="BD1:BJ1"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="A79:A86"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B65:B66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
